--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340026</v>
       </c>
       <c r="B2" t="n">
-        <v>92742</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340024</v>
       </c>
       <c r="B3" t="n">
-        <v>91472</v>
+        <v>91484</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340026</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340024</v>
       </c>
       <c r="B3" t="n">
-        <v>91484</v>
+        <v>91486</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -885,6 +885,782 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128791256</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>769546</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7288326</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>128791255</v>
+      </c>
+      <c r="B5" t="n">
+        <v>78846</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>769545</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7288297</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128791248</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92949</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>769540</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7288303</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128791267</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92756</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>769491</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7288266</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128791249</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92949</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2079</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nordtagging</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Odonticium romellii</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(S.Lundell) Parmasto</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>769560</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7288322</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128791233</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90499</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>769559</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7288320</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128791231</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91388</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>3242</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vitplätt</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Chaetodermella luna</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>769567</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7288319</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128791251</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78847</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tjädermyrslyet, Nb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>769546</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7288326</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-09-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Goldkuhl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340026</v>
       </c>
       <c r="B2" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340024</v>
       </c>
       <c r="B3" t="n">
-        <v>91486</v>
+        <v>91487</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92756</v>
+        <v>92757</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>92949</v>
+        <v>92950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>91388</v>
+        <v>91389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128791256</v>
       </c>
       <c r="B4" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128791255</v>
       </c>
       <c r="B5" t="n">
-        <v>78846</v>
+        <v>78873</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>92950</v>
+        <v>92977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>92950</v>
+        <v>92977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90499</v>
+        <v>90526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>91389</v>
+        <v>91416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128791251</v>
       </c>
       <c r="B11" t="n">
-        <v>78847</v>
+        <v>78874</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340026</v>
       </c>
       <c r="B2" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340024</v>
       </c>
       <c r="B3" t="n">
-        <v>91487</v>
+        <v>91514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128791256</v>
       </c>
       <c r="B4" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128791255</v>
       </c>
       <c r="B5" t="n">
-        <v>78873</v>
+        <v>78877</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>92977</v>
+        <v>92982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>92977</v>
+        <v>92982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>91416</v>
+        <v>91421</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128791251</v>
       </c>
       <c r="B11" t="n">
-        <v>78874</v>
+        <v>78878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340026</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340024</v>
       </c>
       <c r="B3" t="n">
-        <v>91514</v>
+        <v>91524</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>92982</v>
+        <v>92989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>92982</v>
+        <v>92989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B10" t="n">
-        <v>91421</v>
+        <v>78878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R10" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B11" t="n">
-        <v>78878</v>
+        <v>91426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R11" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>78878</v>
+        <v>91426</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R10" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B11" t="n">
-        <v>91426</v>
+        <v>78878</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R11" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B10" t="n">
-        <v>91426</v>
+        <v>78878</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R10" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B11" t="n">
-        <v>78878</v>
+        <v>91426</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R11" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128791256</v>
       </c>
       <c r="B4" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128791255</v>
       </c>
       <c r="B5" t="n">
-        <v>78877</v>
+        <v>78881</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>92989</v>
+        <v>92993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>78878</v>
+        <v>91430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R10" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B11" t="n">
-        <v>91426</v>
+        <v>78882</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R11" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128340026</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>128340024</v>
       </c>
       <c r="B3" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128791256</v>
       </c>
       <c r="B4" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128791255</v>
       </c>
       <c r="B5" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>92993</v>
+        <v>92998</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B10" t="n">
-        <v>91430</v>
+        <v>78787</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R10" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B11" t="n">
-        <v>78882</v>
+        <v>91435</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R11" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>93006</v>
+        <v>93011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>91442</v>
+        <v>91445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128791256</v>
       </c>
       <c r="B4" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128791255</v>
       </c>
       <c r="B5" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>93011</v>
+        <v>93014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>91445</v>
+        <v>91448</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128791251</v>
       </c>
       <c r="B11" t="n">
-        <v>78792</v>
+        <v>78793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128791256</v>
       </c>
       <c r="B4" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128791255</v>
       </c>
       <c r="B5" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>93014</v>
+        <v>93022</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B10" t="n">
-        <v>91448</v>
+        <v>78797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R10" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B11" t="n">
-        <v>78793</v>
+        <v>91454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R11" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>78797</v>
+        <v>91454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R10" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B11" t="n">
-        <v>91454</v>
+        <v>78797</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R11" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>93022</v>
+        <v>93029</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B10" t="n">
-        <v>91454</v>
+        <v>78797</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R10" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B11" t="n">
-        <v>78797</v>
+        <v>91461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R11" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -890,7 +890,7 @@
         <v>128791256</v>
       </c>
       <c r="B4" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>128791255</v>
       </c>
       <c r="B5" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>93029</v>
+        <v>93031</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>128791251</v>
       </c>
       <c r="B10" t="n">
-        <v>78797</v>
+        <v>78799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>128791231</v>
       </c>
       <c r="B11" t="n">
-        <v>91461</v>
+        <v>91463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -1469,10 +1469,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128791251</v>
+        <v>128791231</v>
       </c>
       <c r="B10" t="n">
-        <v>78799</v>
+        <v>91463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1480,21 +1480,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>3242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>769546</v>
+        <v>769567</v>
       </c>
       <c r="R10" t="n">
-        <v>7288326</v>
+        <v>7288319</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1566,10 +1566,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128791231</v>
+        <v>128791251</v>
       </c>
       <c r="B11" t="n">
-        <v>91463</v>
+        <v>78799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1577,21 +1577,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3242</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>769567</v>
+        <v>769546</v>
       </c>
       <c r="R11" t="n">
-        <v>7288319</v>
+        <v>7288326</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 45421-2025 artfynd.xlsx
+++ b/artfynd/A 45421-2025 artfynd.xlsx
@@ -1084,7 +1084,7 @@
         <v>128791248</v>
       </c>
       <c r="B6" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>128791267</v>
       </c>
       <c r="B7" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,7 +1278,7 @@
         <v>128791249</v>
       </c>
       <c r="B8" t="n">
-        <v>93031</v>
+        <v>91592</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
         <v>128791233</v>
       </c>
       <c r="B9" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
